--- a/begunici/app_types/animals/excel_templates/archive_acts/prirezka.xlsx
+++ b/begunici/app_types/animals/excel_templates/archive_acts/prirezka.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\begunici\begunici\app_types\animals\excel_templates\archive_acts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900A2142-6A6C-42C0-8D8A-DFB8EEF69D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B846D4E-D2E2-4A72-9EEE-159D45F367E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>по ОКПО</t>
-  </si>
-  <si>
-    <t>ООО "Бегуницы"</t>
   </si>
   <si>
     <t>Организация</t>
@@ -189,6 +186,9 @@
     <t>Воз-
 раст,
 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ООО "Ферма "Бегуницы"												</t>
   </si>
 </sst>
 </file>
@@ -718,6 +718,125 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -725,129 +844,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1177,115 +1177,115 @@
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.45">
       <c r="AI1" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.45">
       <c r="AI2" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.45">
       <c r="AI3" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="X4" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-      <c r="AC4" s="47"/>
+      <c r="X4" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="42"/>
     </row>
     <row r="5" spans="1:42" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="U5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN5" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="AO5" s="49"/>
-      <c r="AP5" s="50"/>
+      <c r="AN5" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO5" s="44"/>
+      <c r="AP5" s="45"/>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="U6" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="51"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="51"/>
-      <c r="AE6" s="51"/>
-      <c r="AJ6" s="36" t="s">
+      <c r="U6" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="AK6" s="36"/>
-      <c r="AL6" s="36"/>
-      <c r="AN6" s="52" t="s">
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="46"/>
+      <c r="Z6" s="46"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="46"/>
+      <c r="AC6" s="46"/>
+      <c r="AD6" s="46"/>
+      <c r="AE6" s="46"/>
+      <c r="AJ6" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="AO6" s="53"/>
-      <c r="AP6" s="54"/>
+      <c r="AK6" s="47"/>
+      <c r="AL6" s="47"/>
+      <c r="AN6" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO6" s="49"/>
+      <c r="AP6" s="50"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="AJ7" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK7" s="36"/>
-      <c r="AL7" s="36"/>
+      <c r="AJ7" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK7" s="47"/>
+      <c r="AL7" s="47"/>
       <c r="AN7" s="21"/>
       <c r="AO7" s="20"/>
       <c r="AP7" s="19"/>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="36" t="s">
+      <c r="F8" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="24"/>
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="AL8" s="36"/>
+      <c r="AL8" s="47"/>
       <c r="AN8" s="38"/>
       <c r="AO8" s="39"/>
       <c r="AP8" s="40"/>
@@ -1294,36 +1294,36 @@
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="37"/>
-      <c r="AF9" s="37"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="37"/>
-      <c r="AI9" s="37"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="37"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="24"/>
       <c r="AN9" s="38"/>
       <c r="AO9" s="39"/>
       <c r="AP9" s="40"/>
@@ -1332,42 +1332,42 @@
       <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="37"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="37"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="37"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37"/>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="37"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="24"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="24"/>
+      <c r="AL10" s="24"/>
       <c r="AN10" s="38"/>
       <c r="AO10" s="39"/>
       <c r="AP10" s="40"/>
@@ -1376,39 +1376,39 @@
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="45"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="45"/>
-      <c r="Z11" s="45"/>
-      <c r="AA11" s="45"/>
-      <c r="AB11" s="45"/>
-      <c r="AC11" s="45"/>
-      <c r="AD11" s="45"/>
-      <c r="AE11" s="45"/>
-      <c r="AF11" s="45"/>
-      <c r="AG11" s="45"/>
-      <c r="AH11" s="45"/>
-      <c r="AI11" s="45"/>
-      <c r="AJ11" s="45"/>
-      <c r="AK11" s="45"/>
-      <c r="AL11" s="45"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="58"/>
+      <c r="R11" s="58"/>
+      <c r="S11" s="58"/>
+      <c r="T11" s="58"/>
+      <c r="U11" s="58"/>
+      <c r="V11" s="58"/>
+      <c r="W11" s="58"/>
+      <c r="X11" s="58"/>
+      <c r="Y11" s="58"/>
+      <c r="Z11" s="58"/>
+      <c r="AA11" s="58"/>
+      <c r="AB11" s="58"/>
+      <c r="AC11" s="58"/>
+      <c r="AD11" s="58"/>
+      <c r="AE11" s="58"/>
+      <c r="AF11" s="58"/>
+      <c r="AG11" s="58"/>
+      <c r="AH11" s="58"/>
+      <c r="AI11" s="58"/>
+      <c r="AJ11" s="58"/>
+      <c r="AK11" s="58"/>
+      <c r="AL11" s="58"/>
       <c r="AN11" s="38"/>
       <c r="AO11" s="39"/>
       <c r="AP11" s="40"/>
@@ -1417,158 +1417,158 @@
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="37"/>
-      <c r="AF12" s="37"/>
-      <c r="AG12" s="37"/>
-      <c r="AH12" s="37"/>
-      <c r="AI12" s="37"/>
-      <c r="AJ12" s="37"/>
-      <c r="AK12" s="37"/>
-      <c r="AL12" s="37"/>
-      <c r="AN12" s="66"/>
-      <c r="AO12" s="67"/>
-      <c r="AP12" s="68"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
+      <c r="AH12" s="24"/>
+      <c r="AI12" s="24"/>
+      <c r="AJ12" s="24"/>
+      <c r="AK12" s="24"/>
+      <c r="AL12" s="24"/>
+      <c r="AN12" s="25"/>
+      <c r="AO12" s="26"/>
+      <c r="AP12" s="27"/>
     </row>
     <row r="13" spans="1:42" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="14" spans="1:42" ht="49.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="41" t="s">
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="43"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="37"/>
       <c r="M14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="41" t="s">
+      <c r="N14" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="R14" s="42"/>
-      <c r="S14" s="43"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="37"/>
       <c r="T14" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="U14" s="44" t="s">
+      <c r="U14" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="44"/>
-      <c r="W14" s="44"/>
-      <c r="X14" s="44" t="s">
+      <c r="V14" s="57"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="Y14" s="44"/>
-      <c r="Z14" s="44"/>
-      <c r="AA14" s="63" t="s">
+      <c r="Y14" s="57"/>
+      <c r="Z14" s="57"/>
+      <c r="AA14" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="AB14" s="63"/>
-      <c r="AC14" s="63"/>
-      <c r="AD14" s="63"/>
-      <c r="AE14" s="64" t="s">
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="AF14" s="65"/>
-      <c r="AG14" s="65"/>
-      <c r="AH14" s="65" t="s">
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="31"/>
+      <c r="AH14" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="AI14" s="65"/>
-      <c r="AJ14" s="62" t="s">
+      <c r="AI14" s="31"/>
+      <c r="AJ14" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="62"/>
-      <c r="AM14" s="62"/>
-      <c r="AN14" s="65" t="s">
+      <c r="AK14" s="32"/>
+      <c r="AL14" s="32"/>
+      <c r="AM14" s="32"/>
+      <c r="AN14" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="AO14" s="65"/>
-      <c r="AP14" s="65"/>
+      <c r="AO14" s="31"/>
+      <c r="AP14" s="31"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="A15" s="55"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="59"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="63"/>
       <c r="M15" s="15"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="61"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="33"/>
       <c r="T15" s="16"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-      <c r="AA15" s="31"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="32"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="34"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="35"/>
-      <c r="AL15" s="35"/>
-      <c r="AM15" s="35"/>
-      <c r="AN15" s="60"/>
-      <c r="AO15" s="60"/>
-      <c r="AP15" s="60"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="34"/>
+      <c r="W15" s="34"/>
+      <c r="X15" s="34"/>
+      <c r="Y15" s="34"/>
+      <c r="Z15" s="34"/>
+      <c r="AA15" s="53"/>
+      <c r="AB15" s="34"/>
+      <c r="AC15" s="34"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="55"/>
+      <c r="AF15" s="56"/>
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="56"/>
+      <c r="AI15" s="56"/>
+      <c r="AJ15" s="56"/>
+      <c r="AK15" s="56"/>
+      <c r="AL15" s="56"/>
+      <c r="AM15" s="56"/>
+      <c r="AN15" s="28"/>
+      <c r="AO15" s="28"/>
+      <c r="AP15" s="28"/>
     </row>
     <row r="17" spans="1:42" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
@@ -1689,140 +1689,140 @@
       <c r="AP21" s="10"/>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
       <c r="K22" s="8"/>
-      <c r="L22" s="24" t="s">
+      <c r="L22" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
       <c r="S22" s="8"/>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
-      <c r="V22" s="24" t="s">
+      <c r="V22" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="65"/>
       <c r="Y22" s="8"/>
-      <c r="Z22" s="24" t="s">
+      <c r="Z22" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="24"/>
-      <c r="AE22" s="24"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="65"/>
       <c r="AF22" s="8"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="8"/>
       <c r="AJ22" s="8"/>
       <c r="AK22" s="8"/>
-      <c r="AL22" s="25"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="25"/>
-      <c r="AO22" s="25"/>
-      <c r="AP22" s="25"/>
+      <c r="AL22" s="66"/>
+      <c r="AM22" s="66"/>
+      <c r="AN22" s="66"/>
+      <c r="AO22" s="66"/>
+      <c r="AP22" s="66"/>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A24" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
       <c r="J24" s="10"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
       <c r="T24" s="12"/>
-      <c r="W24" s="27"/>
-      <c r="X24" s="27"/>
+      <c r="W24" s="64"/>
+      <c r="X24" s="64"/>
       <c r="Y24" s="10"/>
-      <c r="Z24" s="27"/>
-      <c r="AA24" s="27"/>
-      <c r="AB24" s="27"/>
-      <c r="AC24" s="27"/>
-      <c r="AD24" s="27"/>
-      <c r="AE24" s="27"/>
-      <c r="AG24" s="28"/>
-      <c r="AH24" s="28"/>
-      <c r="AI24" s="28"/>
+      <c r="Z24" s="64"/>
+      <c r="AA24" s="64"/>
+      <c r="AB24" s="64"/>
+      <c r="AC24" s="64"/>
+      <c r="AD24" s="64"/>
+      <c r="AE24" s="64"/>
+      <c r="AG24" s="68"/>
+      <c r="AH24" s="68"/>
+      <c r="AI24" s="68"/>
       <c r="AJ24" s="10"/>
       <c r="AK24" s="10"/>
-      <c r="AL24" s="27"/>
-      <c r="AM24" s="27"/>
-      <c r="AN24" s="27"/>
-      <c r="AO24" s="27"/>
-      <c r="AP24" s="27"/>
+      <c r="AL24" s="64"/>
+      <c r="AM24" s="64"/>
+      <c r="AN24" s="64"/>
+      <c r="AO24" s="64"/>
+      <c r="AP24" s="64"/>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.45">
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
       <c r="J25" s="8"/>
-      <c r="K25" s="24" t="s">
+      <c r="K25" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
       <c r="S25" s="8"/>
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
-      <c r="W25" s="25"/>
-      <c r="X25" s="25"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="66"/>
       <c r="Y25" s="8"/>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="25"/>
-      <c r="AB25" s="25"/>
-      <c r="AC25" s="25"/>
-      <c r="AD25" s="25"/>
-      <c r="AE25" s="25"/>
+      <c r="Z25" s="66"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="66"/>
+      <c r="AC25" s="66"/>
+      <c r="AD25" s="66"/>
+      <c r="AE25" s="66"/>
       <c r="AF25" s="8"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8"/>
       <c r="AJ25" s="8"/>
       <c r="AK25" s="8"/>
-      <c r="AL25" s="25"/>
-      <c r="AM25" s="25"/>
-      <c r="AN25" s="25"/>
-      <c r="AO25" s="25"/>
-      <c r="AP25" s="25"/>
+      <c r="AL25" s="66"/>
+      <c r="AM25" s="66"/>
+      <c r="AN25" s="66"/>
+      <c r="AO25" s="66"/>
+      <c r="AP25" s="66"/>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.45">
       <c r="C26" s="8"/>
@@ -1874,49 +1874,39 @@
       <c r="H27" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
       <c r="O27" s="4">
         <v>20</v>
       </c>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
       <c r="R27" s="2" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="E12:AL12"/>
-    <mergeCell ref="AN12:AP12"/>
-    <mergeCell ref="AN15:AP15"/>
-    <mergeCell ref="AA14:AD14"/>
-    <mergeCell ref="AE14:AG14"/>
-    <mergeCell ref="AH14:AI14"/>
-    <mergeCell ref="AJ14:AM14"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="AN11:AP11"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AN5:AP5"/>
-    <mergeCell ref="U6:AE6"/>
-    <mergeCell ref="AJ6:AL6"/>
-    <mergeCell ref="AN6:AP6"/>
-    <mergeCell ref="AN8:AP8"/>
-    <mergeCell ref="I9:AL9"/>
-    <mergeCell ref="AN9:AP9"/>
-    <mergeCell ref="C10:AL10"/>
-    <mergeCell ref="AN10:AP10"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="L22:R22"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="AL22:AP22"/>
+    <mergeCell ref="AL24:AP24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Z25:AE25"/>
+    <mergeCell ref="AL25:AP25"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="K24:R24"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="Z24:AE24"/>
+    <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="I27:N27"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="AA15:AD15"/>
@@ -1933,22 +1923,32 @@
     <mergeCell ref="F11:AL11"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="G15:L15"/>
-    <mergeCell ref="AL24:AP24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:R25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Z25:AE25"/>
-    <mergeCell ref="AL25:AP25"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:R24"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="Z24:AE24"/>
-    <mergeCell ref="AG24:AI24"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="L22:R22"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Z22:AE22"/>
-    <mergeCell ref="AL22:AP22"/>
+    <mergeCell ref="AN11:AP11"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AN5:AP5"/>
+    <mergeCell ref="U6:AE6"/>
+    <mergeCell ref="AJ6:AL6"/>
+    <mergeCell ref="AN6:AP6"/>
+    <mergeCell ref="AN8:AP8"/>
+    <mergeCell ref="I9:AL9"/>
+    <mergeCell ref="AN9:AP9"/>
+    <mergeCell ref="C10:AL10"/>
+    <mergeCell ref="AN10:AP10"/>
+    <mergeCell ref="E12:AL12"/>
+    <mergeCell ref="AN12:AP12"/>
+    <mergeCell ref="AN15:AP15"/>
+    <mergeCell ref="AA14:AD14"/>
+    <mergeCell ref="AE14:AG14"/>
+    <mergeCell ref="AH14:AI14"/>
+    <mergeCell ref="AJ14:AM14"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="N14:P14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
